--- a/tables/rmst_multihorizon_summary.xlsx
+++ b/tables/rmst_multihorizon_summary.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RMST summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Complete dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Retired only" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,42 +459,52 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Capacity (GW)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Maximum follow-up (years)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>KM median (years)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>t80 (years)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Median, t50 (years)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>t10 (years)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>RMST at 10 y</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMST at 20 y</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>RMST at 30 y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>RMST at 40 y</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RMST at 50 y</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>RMST at 60 y</t>
         </is>
       </c>
     </row>
@@ -516,28 +529,32 @@
         <v>1348</v>
       </c>
       <c r="F2" t="n">
+        <v>2287.63</v>
+      </c>
+      <c r="G2" t="n">
         <v>117</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>52</v>
+      </c>
+      <c r="I2" t="n">
         <v>61</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>20</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>29.9</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>39.6</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>48.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>55.7</v>
       </c>
     </row>
     <row r="3">
@@ -561,28 +578,32 @@
         <v>7901</v>
       </c>
       <c r="F3" t="n">
+        <v>1826.47</v>
+      </c>
+      <c r="G3" t="n">
         <v>125</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>45</v>
+      </c>
+      <c r="I3" t="n">
         <v>62</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>19.8</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>29.4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>38.4</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>46.3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>52.7</v>
       </c>
     </row>
     <row r="4">
@@ -606,28 +627,32 @@
         <v>3910</v>
       </c>
       <c r="F4" t="n">
+        <v>193.81</v>
+      </c>
+      <c r="G4" t="n">
         <v>125</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>38</v>
+      </c>
+      <c r="I4" t="n">
         <v>58</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>9.9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>19.5</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>28.5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>36.7</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>43.9</v>
-      </c>
-      <c r="M4" t="n">
-        <v>49.5</v>
       </c>
     </row>
     <row r="5">
@@ -651,25 +676,31 @@
         <v>48763</v>
       </c>
       <c r="F5" t="n">
+        <v>901.95</v>
+      </c>
+      <c r="G5" t="n">
         <v>42</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I5" t="n">
         <v>29</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>19.9</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>27.5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>30.2</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -692,27 +723,33 @@
         <v>16711</v>
       </c>
       <c r="F6" t="n">
+        <v>877.9</v>
+      </c>
+      <c r="G6" t="n">
         <v>55</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>32</v>
+      </c>
+      <c r="I6" t="n">
         <v>36</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>19.7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>28.7</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>34.7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>38.9</v>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -735,21 +772,27 @@
         <v>346</v>
       </c>
       <c r="F7" t="n">
+        <v>80.12</v>
+      </c>
+      <c r="G7" t="n">
         <v>29</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>22</v>
+      </c>
+      <c r="I7" t="n">
         <v>24</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>19.7</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -772,27 +815,33 @@
         <v>419</v>
       </c>
       <c r="F8" t="n">
+        <v>514.2</v>
+      </c>
+      <c r="G8" t="n">
         <v>56</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" t="n">
         <v>45</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>19</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>27.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>34.9</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>40.2</v>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -815,28 +864,32 @@
         <v>4818</v>
       </c>
       <c r="F9" t="n">
+        <v>111.38</v>
+      </c>
+      <c r="G9" t="n">
         <v>125</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>29</v>
+      </c>
+      <c r="I9" t="n">
         <v>68</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
         <v>9.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>19.3</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>27.7</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>35.4</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>42.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>49.7</v>
       </c>
     </row>
     <row r="10">
@@ -860,26 +913,30 @@
         <v>480</v>
       </c>
       <c r="F10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G10" t="n">
         <v>67</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
+        <v>23</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>10</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>19.7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>27.4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>33.2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>38.4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>43.5</v>
       </c>
     </row>
     <row r="11">
@@ -903,26 +960,2226 @@
         <v>7054</v>
       </c>
       <c r="F11" t="n">
+        <v>1193.05</v>
+      </c>
+      <c r="G11" t="n">
         <v>134</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
+        <v>117</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>10</v>
       </c>
+      <c r="L11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Retired assets</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (GW)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum retirement age (years)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>t80 (years)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Median, t50 (years)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>t10 (years)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mean retirement age (years)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RMST at 10 y</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>RMST at 20 y</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMST at 30 y</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMST at 40 y</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>RMST at 50 y</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>635</v>
+      </c>
+      <c r="D2" t="n">
+        <v>106.51</v>
+      </c>
+      <c r="E2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H2" t="n">
+        <v>66</v>
+      </c>
+      <c r="I2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>39</v>
+      </c>
+      <c r="N2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1358</v>
+      </c>
+      <c r="D3" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="E3" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>62</v>
+      </c>
+      <c r="I3" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>27</v>
+      </c>
+      <c r="M3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1391</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="E4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" t="n">
+        <v>63</v>
+      </c>
+      <c r="I4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Solar PV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>168</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>325</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="E6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>226</v>
+      </c>
+      <c r="D8" t="n">
+        <v>115.46</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="n">
+        <v>45</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>527</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Geothermal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>141</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23</v>
+      </c>
+      <c r="H10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hydropower</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>263</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E11" t="n">
+        <v>120</v>
+      </c>
+      <c r="F11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" t="n">
+        <v>86</v>
+      </c>
+      <c r="H11" t="n">
+        <v>110</v>
+      </c>
       <c r="I11" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Horizon (years)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RMST complete dataset (years)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RMST retired only (years)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Difference (years)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMST complete as % of horizon</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RMST retired only as % of horizon</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>20</v>
       </c>
-      <c r="J11" t="n">
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="n">
         <v>29.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="E4" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>97.40000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>76.90000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>95</v>
+      </c>
+      <c r="H14" t="n">
+        <v>84.90000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>40</v>
+      </c>
+      <c r="D15" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>78.09999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fossil fuels</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Solar PV</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Solar PV</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Solar PV</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Solar PV</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>40</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Solar PV</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>72.40000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>50</v>
+      </c>
+      <c r="D26" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>94.40000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>40</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" t="n">
+        <v>19</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>40</v>
+      </c>
+      <c r="D35" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="E35" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Core transition technologies</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>50</v>
+      </c>
+      <c r="D36" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>40</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D41" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Geothermal</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Geothermal</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Geothermal</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Geothermal</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>40</v>
+      </c>
+      <c r="D45" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>83</v>
+      </c>
+      <c r="H45" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Geothermal</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>50</v>
+      </c>
+      <c r="D46" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hydropower</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" t="n">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hydropower</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>20</v>
+      </c>
+      <c r="D48" t="n">
+        <v>20</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>98.40000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hydropower</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>30</v>
+      </c>
+      <c r="D49" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>95.90000000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hydropower</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>40</v>
+      </c>
+      <c r="D50" t="n">
         <v>39.9</v>
       </c>
-      <c r="L11" t="n">
+      <c r="E50" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hydropower</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Other low-carbon technologies</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>50</v>
+      </c>
+      <c r="D51" t="n">
         <v>49.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>59.6</v>
+      <c r="E51" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>87.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Complete dataset</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>All assets; operating assets right-censored at their 2025 age (main-text Fig. 1, Table 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Retired only</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Assets with a recorded retirement only; no censoring (Supplementary Fig. S6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>t80, t50, t10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>First observed age at which the survival curve falls to or below 0.8, 0.5, 0.1; no interpolation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RMST at tau</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Area under the Kaplan-Meier curve from 0 to tau: mean years operated within the first tau years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Blank cells</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Complete dataset: threshold not reached, or tau beyond the maximum observed follow-up. Retired only: threshold not reached. Retired-only RMST is exact at every horizon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RMST of both samples at each horizon; difference = complete minus retired only.</t>
+        </is>
       </c>
     </row>
   </sheetData>
